--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06/29 12:24:17</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>24390.24</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>06/27 13:02:18</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>6329.11</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yyjr86</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>250000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30719.36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>6329.11</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>30719.36</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>06/29 13:49:30</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>24390</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>250000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30719.36</t>
+          <t>250000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30719.36</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>24390</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>30719.36</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6329.36</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/29 12:24:17</t>
+          <t>07/04 15:49:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24390.24</t>
+          <t>20606.06</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,210 +117,252 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06/29 12:24:17</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>24390.24</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>06/27 13:02:18</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>6329.11</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yyjr86</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>06/29 13:49:30</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>24390</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>yyjr0</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>250000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30719.36</t>
+          <t>420000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>51325.42</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>24390</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>6329.36</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>26935.42</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -286,83 +286,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>07/04 17:24:07</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>20606</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>06/29 13:49:30</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>24390</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>yyjr0</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>420000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>51325.42</t>
+          <t>420000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>51325.42</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>44996</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>26935.42</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6329.42</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/04 15:49:59</t>
+          <t>07/15 12:35:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20606.06</t>
+          <t>30487.8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/29 12:24:17</t>
+          <t>07/04 15:49:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>24390.24</t>
+          <t>20606.06</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,237 +159,279 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06/29 12:24:17</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>24390.24</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>06/27 13:02:18</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>6329.11</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>yyjr86</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/04 17:24:07</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>07/04 17:24:07</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20606</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>06/29 13:49:30</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>24390</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>yyjr0</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>420000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>51325.42</t>
+          <t>670000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>44996</t>
+          <t>81813.22</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>44996</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>6329.42</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>36817.22</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/15 12:35:12</t>
+          <t>07/15 13:16:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30487.8</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/04 15:49:59</t>
+          <t>07/15 12:35:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20606.06</t>
+          <t>30487.8</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/29 12:24:17</t>
+          <t>07/04 15:49:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24390.24</t>
+          <t>20606.06</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,237 +201,279 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>06/29 12:24:17</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>24390.24</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>06/27 13:02:18</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>6329.11</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>yyjr86</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/04 17:24:07</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>07/04 17:24:07</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20606</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>06/29 13:49:30</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>24390</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>yyjr0</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>670000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>81813.22</t>
+          <t>760000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>44996</t>
+          <t>92656.6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>44996</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>36817.22</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>47660.6</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -370,12 +370,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/04 17:24:07</t>
+          <t>07/15 14:28:34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -397,83 +397,110 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>07/04 17:24:07</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20606</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>06/29 13:49:30</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>24390</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>yyjr0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>760000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>92656.6</t>
+          <t>760000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>44996</t>
+          <t>92656.6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>86326</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>47660.6</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>6330.6</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/15 13:16:53</t>
+          <t>07/20 13:22:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>105000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>12650.6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/15 12:35:12</t>
+          <t>07/15 13:16:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30487.8</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/04 15:49:59</t>
+          <t>07/15 12:35:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20606.06</t>
+          <t>30487.8</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/29 12:24:17</t>
+          <t>07/04 15:49:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24390.24</t>
+          <t>20606.06</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,166 +243,181 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>06/29 12:24:17</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>24390.24</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>06/27 13:02:18</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>6329.11</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>yyjr86</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/15 14:28:34</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>41330</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/04 17:24:07</t>
+          <t>07/15 14:28:34</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -424,83 +439,110 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>07/04 17:24:07</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20606</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>06/29 13:49:30</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>24390</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>yyjr0</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>760000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>92656.6</t>
+          <t>865000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>86326</t>
+          <t>105307.2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>86326</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>6330.6</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>18981.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -412,12 +412,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/15 14:28:34</t>
+          <t>07/20 15:12:29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>41330</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -427,7 +427,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>yyjr61</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -439,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/04 17:24:07</t>
+          <t>07/15 14:28:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,83 +466,110 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>07/04 17:24:07</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>20606</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>06/29 13:49:30</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>24390</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>yyjr0</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>865000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>105307.2</t>
+          <t>865000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>86326</t>
+          <t>105307.2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>98976</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>18981.2</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>6331.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/20 13:22:58</t>
+          <t>07/20 16:18:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>105000</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12650.6</t>
+          <t>7738.1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/15 13:16:53</t>
+          <t>07/20 13:22:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>105000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>12650.6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/15 12:35:12</t>
+          <t>07/15 13:16:53</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30487.8</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/04 15:49:59</t>
+          <t>07/15 12:35:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20606.06</t>
+          <t>30487.8</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/29 12:24:17</t>
+          <t>07/04 15:49:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24390.24</t>
+          <t>20606.06</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,166 +285,181 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>06/29 12:24:17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>24390.24</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>06/27 13:02:18</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>6329.11</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>yyjr86</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/20 15:12:29</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>yyjr61</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/15 14:28:34</t>
+          <t>07/20 15:12:29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>41330</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -454,7 +469,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>yyjr61</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -466,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/04 17:24:07</t>
+          <t>07/15 14:28:34</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -493,83 +508,110 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>07/04 17:24:07</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>20606</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>06/29 13:49:30</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>24390</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>yyjr0</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>865000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>105307.2</t>
+          <t>930000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>98976</t>
+          <t>113045.29</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>98976</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>6331.2</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>14069.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -454,12 +454,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/20 15:12:29</t>
+          <t>07/20 17:52:15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -469,7 +469,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>yyjr61</t>
+          <t>yyjr0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -481,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/15 14:28:34</t>
+          <t>07/20 15:12:29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>41330</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>yyjr61</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -508,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/04 17:24:07</t>
+          <t>07/15 14:28:34</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -535,83 +535,110 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>07/04 17:24:07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20606</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>06/29 13:49:30</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>24390</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>yyjr0</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>930000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>113045.29</t>
+          <t>930000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>98976</t>
+          <t>113045.29</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>106526</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>14069.29</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>6519.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -454,12 +454,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/20 17:52:15</t>
+          <t>07/20 17:52:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -481,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/20 15:12:29</t>
+          <t>07/20 17:52:15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>yyjr61</t>
+          <t>yyjr0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -508,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/15 14:28:34</t>
+          <t>07/20 15:12:29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>41330</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>yyjr61</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/04 17:24:07</t>
+          <t>07/15 14:28:34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -562,83 +562,110 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>07/04 17:24:07</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>20606</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>06/29 13:49:30</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>24390</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>yyjr0</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>930000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>113045.29</t>
+          <t>930000</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>106526</t>
+          <t>113045.29</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>106714</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>6519.29</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>6331.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/20 16:18:00</t>
+          <t>07/31 12:29:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>65000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7738.1</t>
+          <t>7594.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>yyjr6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/20 13:22:58</t>
+          <t>07/20 16:18:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>105000</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12650.6</t>
+          <t>7738.1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/15 13:16:53</t>
+          <t>07/20 13:22:58</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>105000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>12650.6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/15 12:35:12</t>
+          <t>07/15 13:16:53</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30487.8</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/04 15:49:59</t>
+          <t>07/15 12:35:12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20606.06</t>
+          <t>30487.8</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/29 12:24:17</t>
+          <t>07/04 15:49:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>24390.24</t>
+          <t>20606.06</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,166 +327,181 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>06/29 12:24:17</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>24390.24</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>06/27 13:02:18</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>6329.11</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>yyjr86</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/20 17:52:26</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/20 17:52:15</t>
+          <t>07/20 17:52:26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -508,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/20 15:12:29</t>
+          <t>07/20 17:52:15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -523,7 +538,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>yyjr61</t>
+          <t>yyjr0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -535,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/15 14:28:34</t>
+          <t>07/20 15:12:29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>41330</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -550,7 +565,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>yyjr61</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -562,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/04 17:24:07</t>
+          <t>07/15 14:28:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -589,83 +604,110 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>07/04 17:24:07</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20606</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>06/29 13:49:30</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>24390</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>yyjr0</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>930000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>113045.29</t>
+          <t>990000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>106714</t>
+          <t>120640.23</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>106714</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>6331.29</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>13926.23</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -496,12 +496,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/20 17:52:26</t>
+          <t>07/31 16:13:36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -523,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/20 17:52:15</t>
+          <t>07/20 17:52:26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -550,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/20 15:12:29</t>
+          <t>07/20 17:52:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>yyjr61</t>
+          <t>yyjr0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -577,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/15 14:28:34</t>
+          <t>07/20 15:12:29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>41330</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>yyjr61</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -604,12 +604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/04 17:24:07</t>
+          <t>07/15 14:28:34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -631,83 +631,110 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>07/04 17:24:07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>20606</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>06/29 13:49:30</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>24390</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>yyjr0</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>990000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>120640.23</t>
+          <t>990000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>106714</t>
+          <t>120640.23</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>114308</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>13926.23</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>6332.23</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/31 12:29:51</t>
+          <t>08/02 13:24:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7594.94</t>
+          <t>5063.29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/20 16:18:00</t>
+          <t>07/31 12:29:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>65000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7738.1</t>
+          <t>7594.94</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>yyjr6</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/20 13:22:58</t>
+          <t>07/20 16:18:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>105000</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12650.6</t>
+          <t>7738.1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/15 13:16:53</t>
+          <t>07/20 13:22:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>105000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>12650.6</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/15 12:35:12</t>
+          <t>07/15 13:16:53</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30487.8</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/04 15:49:59</t>
+          <t>07/15 12:35:12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20606.06</t>
+          <t>30487.8</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/29 12:24:17</t>
+          <t>07/04 15:49:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24390.24</t>
+          <t>20606.06</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,166 +369,181 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>06/29 12:24:17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>24390.24</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>06/27 13:02:18</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>6329.11</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>yyjr86</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/31 16:13:36</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/20 17:52:26</t>
+          <t>07/31 16:13:36</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -550,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/20 17:52:15</t>
+          <t>07/20 17:52:26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -577,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/20 15:12:29</t>
+          <t>07/20 17:52:15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -592,7 +607,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>yyjr61</t>
+          <t>yyjr0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -604,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/15 14:28:34</t>
+          <t>07/20 15:12:29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>41330</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -619,7 +634,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>yyjr61</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -631,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/04 17:24:07</t>
+          <t>07/15 14:28:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -658,83 +673,110 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>07/04 17:24:07</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20606</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>06/29 13:49:30</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>24390</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>yyjr0</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>990000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>120640.23</t>
+          <t>1030000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>114308</t>
+          <t>125703.52</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>114308</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>6332.23</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>11395.52</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/02 13:24:47</t>
+          <t>08/03 12:29:38</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5063.29</t>
+          <t>10562.41</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/31 12:29:51</t>
+          <t>08/02 13:24:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7594.94</t>
+          <t>5063.29</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/20 16:18:00</t>
+          <t>07/31 12:29:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7738.1</t>
+          <t>7594.94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>yyjr6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/20 13:22:58</t>
+          <t>07/20 16:18:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>105000</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12650.6</t>
+          <t>7738.1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/15 13:16:53</t>
+          <t>07/20 13:22:58</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>105000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>12650.6</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/15 12:35:12</t>
+          <t>07/15 13:16:53</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30487.8</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/04 15:49:59</t>
+          <t>07/15 12:35:12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20606.06</t>
+          <t>30487.8</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/29 12:24:17</t>
+          <t>07/04 15:49:59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24390.24</t>
+          <t>20606.06</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,166 +411,181 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>06/29 12:24:17</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>24390.24</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>06/27 13:02:18</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>6329.11</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>yyjr86</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/31 16:13:36</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/20 17:52:26</t>
+          <t>07/31 16:13:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -592,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/20 17:52:15</t>
+          <t>07/20 17:52:26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -619,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/20 15:12:29</t>
+          <t>07/20 17:52:15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -634,7 +649,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>yyjr61</t>
+          <t>yyjr0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -646,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/15 14:28:34</t>
+          <t>07/20 15:12:29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>41330</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -661,7 +676,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>yyjr61</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -673,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/04 17:24:07</t>
+          <t>07/15 14:28:34</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -700,83 +715,110 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>07/04 17:24:07</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>20606</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>06/29 13:49:30</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>24390</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>yyjr0</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1030000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>125703.52</t>
+          <t>1113443</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>114308</t>
+          <t>136265.93</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>114308</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>11395.52</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>21957.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/31 16:13:36</t>
+          <t>08/03 16:04:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>10562</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>yyjr4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/20 17:52:26</t>
+          <t>07/31 16:13:36</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/20 17:52:15</t>
+          <t>07/20 17:52:26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/20 15:12:29</t>
+          <t>07/20 17:52:15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>yyjr61</t>
+          <t>yyjr0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/15 14:28:34</t>
+          <t>07/20 15:12:29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>41330</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>yyjr61</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/04 17:24:07</t>
+          <t>07/15 14:28:34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,83 +742,110 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>07/04 17:24:07</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>20606</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>06/29 13:49:30</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>24390</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>yyjr0</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1113443</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>136265.93</t>
+          <t>1113443</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>114308</t>
+          <t>136265.93</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>124870</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>21957.93</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>11395.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
+++ b/bills/JXZFSP/-1003973048495/350c5bfb689fe578d9250d112466c6734313008d13d5e4f0eee229bc3f0fc246/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/03 12:29:38</t>
+          <t>08/05 15:00:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>83443</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10562.41</t>
+          <t>12658.23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/02 13:24:47</t>
+          <t>08/03 12:29:38</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5063.29</t>
+          <t>10562.41</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/31 12:29:51</t>
+          <t>08/02 13:24:47</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7594.94</t>
+          <t>5063.29</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/20 16:18:00</t>
+          <t>07/31 12:29:51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>65000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7738.1</t>
+          <t>7594.94</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>yyjr6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/20 13:22:58</t>
+          <t>07/20 16:18:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>105000</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12650.6</t>
+          <t>7738.1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/15 13:16:53</t>
+          <t>07/20 13:22:58</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>105000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>12650.6</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/15 12:35:12</t>
+          <t>07/15 13:16:53</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30487.8</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/04 15:49:59</t>
+          <t>07/15 12:35:12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20606.06</t>
+          <t>30487.8</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/29 12:24:17</t>
+          <t>07/04 15:49:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>24390.24</t>
+          <t>20606.06</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,166 +453,181 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>06/29 12:24:17</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>24390.24</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>06/27 13:02:18</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>6329.11</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>yyjr86</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/03 16:04:33</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10562</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>yyjr4</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/31 16:13:36</t>
+          <t>08/03 16:04:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>10562</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -622,7 +637,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>yyjr4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -634,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/20 17:52:26</t>
+          <t>07/31 16:13:36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/20 17:52:15</t>
+          <t>07/20 17:52:26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -688,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/20 15:12:29</t>
+          <t>07/20 17:52:15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -703,7 +718,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>yyjr61</t>
+          <t>yyjr0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -715,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/15 14:28:34</t>
+          <t>07/20 15:12:29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>41330</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -730,7 +745,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>yyjr0</t>
+          <t>yyjr61</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -742,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/04 17:24:07</t>
+          <t>07/15 14:28:34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -769,83 +784,110 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>07/04 17:24:07</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>20606</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>06/29 13:49:30</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>24390</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>yyjr0</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>yyjr0</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1113443</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>136265.93</t>
+          <t>1213443</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>124870</t>
+          <t>148924.16</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>124870</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>11395.93</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>24054.16</t>
         </is>
       </c>
     </row>
